--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.96715807415256</v>
+        <v>9.907163187049791</v>
       </c>
       <c r="D2" t="n">
-        <v>60.29090356380892</v>
+        <v>9.79727182911895</v>
       </c>
       <c r="E2" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F2" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.3810469561916</v>
+        <v>11.11192013038113</v>
       </c>
       <c r="D3" t="n">
-        <v>69.05273261189437</v>
+        <v>11.22106904943284</v>
       </c>
       <c r="E3" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F3" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.62745818967342</v>
+        <v>10.66446195582193</v>
       </c>
       <c r="D4" t="n">
-        <v>64.6637692232575</v>
+        <v>10.50786249877934</v>
       </c>
       <c r="E4" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F4" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.02932816230586</v>
+        <v>10.4047658263747</v>
       </c>
       <c r="D5" t="n">
-        <v>63.15135751229239</v>
+        <v>10.26209559574751</v>
       </c>
       <c r="E5" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F5" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.86817493902816</v>
+        <v>8.753578427592076</v>
       </c>
       <c r="D6" t="n">
-        <v>54.10203307823927</v>
+        <v>8.791580375213881</v>
       </c>
       <c r="E6" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F6" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>74.59410451254168</v>
+        <v>12.12154198328802</v>
       </c>
       <c r="D7" t="n">
-        <v>75.47735210354442</v>
+        <v>12.26506971682597</v>
       </c>
       <c r="E7" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F7" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.87313896186637</v>
+        <v>6.966885081303286</v>
       </c>
       <c r="D8" t="n">
-        <v>43.08913958853493</v>
+        <v>7.001985183136927</v>
       </c>
       <c r="E8" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F8" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.19757877980945</v>
+        <v>5.557106551719035</v>
       </c>
       <c r="D9" t="n">
-        <v>33.15580652860724</v>
+        <v>5.387818560898676</v>
       </c>
       <c r="E9" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F9" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.28101450728404</v>
+        <v>4.108164857433657</v>
       </c>
       <c r="D10" t="n">
-        <v>23.95905450293251</v>
+        <v>3.893346356726533</v>
       </c>
       <c r="E10" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F10" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.30049130903188</v>
+        <v>6.548829837717681</v>
       </c>
       <c r="D11" t="n">
-        <v>39.47368185405154</v>
+        <v>6.414473301283376</v>
       </c>
       <c r="E11" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F11" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.93521571590116</v>
+        <v>5.676972553833939</v>
       </c>
       <c r="D12" t="n">
-        <v>33.71537338142256</v>
+        <v>5.478748174481166</v>
       </c>
       <c r="E12" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F12" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>17.99111559982088</v>
+        <v>2.923556284970893</v>
       </c>
       <c r="D13" t="n">
-        <v>16.94922681472217</v>
+        <v>2.754249357392352</v>
       </c>
       <c r="E13" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F13" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.70567611186304</v>
+        <v>5.802172368177745</v>
       </c>
       <c r="D14" t="n">
-        <v>37.00514271463182</v>
+        <v>6.013335691127671</v>
       </c>
       <c r="E14" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F14" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.869734951610477</v>
+        <v>1.441331929636703</v>
       </c>
       <c r="D15" t="n">
-        <v>8.547050115141426</v>
+        <v>1.388895643710482</v>
       </c>
       <c r="E15" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F15" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.72694512497902</v>
+        <v>3.693128582809091</v>
       </c>
       <c r="D16" t="n">
-        <v>23.68481161145289</v>
+        <v>3.848781886861094</v>
       </c>
       <c r="E16" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F16" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.74075845911815</v>
+        <v>4.6703732496067</v>
       </c>
       <c r="D17" t="n">
-        <v>29.34842087231351</v>
+        <v>4.769118391750946</v>
       </c>
       <c r="E17" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F17" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>44.04022116859506</v>
+        <v>7.156535939896697</v>
       </c>
       <c r="D18" t="n">
-        <v>45.07186604427857</v>
+        <v>7.324178232195268</v>
       </c>
       <c r="E18" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F18" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.43680208326837</v>
+        <v>6.73348033853111</v>
       </c>
       <c r="D19" t="n">
-        <v>42.24418122156622</v>
+        <v>6.864679448504511</v>
       </c>
       <c r="E19" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F19" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>85.31686004794277</v>
+        <v>13.8639897577907</v>
       </c>
       <c r="D20" t="n">
-        <v>86.3798049792362</v>
+        <v>14.03671830912588</v>
       </c>
       <c r="E20" t="n">
-        <v>20.12660811381492</v>
+        <v>3.270573818494924</v>
       </c>
       <c r="F20" t="n">
-        <v>20.36747033021366</v>
+        <v>3.30971392865972</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
